--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Nexus_Uprising_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Nexus_Uprising_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R853f277f4c954d23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R8ca617ec336849f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rf636f4f20a5f4e86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rb655ac7d2bd241f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rbe7fa5b826ba40e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Re69f8577681f48ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R538da742a4e5454c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rb622495dac514e68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R17c1f31fcf0b4ef3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R477e40e9ca0040fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R884b7cdd756c48b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R971acd8dcf0d4e67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R36ff7223f3df4514"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rcbfa199bace54dd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rca736e50d2514a79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R4fbc568d0fc84610"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Ra5dbcfa889da44ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R1603617ad91f482e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rd119e2ec2b504802"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Ree7a19b48d5b4467"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R13218d7230924b97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rb4ebe5c22dce4ccc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rd71e4e8dea884fa4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R50896ce5c76e4ff1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R62fb71d20c114869"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R8ab27ff53ca94a0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R7b8e586e93964fa6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R001ea0da4b8844c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rfda1c2f5f8af486b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rfc4673e34a0f4e66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Ra68be84f58744001"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R566babc1bd274ddd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rcefb50e6f5bd4d9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rde261e969ce04590"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rfff6819604094b99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Ref062ccb16774ee2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R42fc06e86e964638"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R17cf87c44d054641"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rd18ecf30c04745f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R5696c6d7064b4298"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Ra2f262663a0b46c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R2dade13e15ab45cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R20d40c54772540e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R1f2f0a9460f94edf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rf61a0c18aaff4794"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R00dc3e428e8947c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R6bb878db564f4f06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R2eec4a5a679c4593"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R628692150d2f42a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R41273ec6ed914ca9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rce3b9d3d9ef44769"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R2e4849eb1d224a3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R8dd261115cff4449"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R06b0d75292844b74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R0c1e8bc6b25f45b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R66c3b6573e554183"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="46">
+  <x:cellXfs count="44">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -230,12 +230,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -2039,7 +2033,7 @@
       <x:c r="A5" s="2" t="str">
         <x:v>Fiches suivies</x:v>
       </x:c>
-      <x:c r="B5" s="34" t="n">
+      <x:c r="B5" s="32" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>159</x:v>
       </x:c>
@@ -2047,7 +2041,7 @@
       <x:c r="D5" s="2" t="str">
         <x:v>Intégrés</x:v>
       </x:c>
-      <x:c r="E5" s="34" t="n">
+      <x:c r="E5" s="32" t="n">
         <x:f>SUM(E10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2055,7 +2049,7 @@
       <x:c r="G5" s="2" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="H5" s="34" t="n">
+      <x:c r="H5" s="32" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -2063,7 +2057,7 @@
       <x:c r="J5" s="2" t="str">
         <x:v>Extrapolations</x:v>
       </x:c>
-      <x:c r="K5" s="34" t="n">
+      <x:c r="K5" s="32" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>131</x:v>
       </x:c>
@@ -2086,7 +2080,7 @@
       <x:c r="M6" s="2"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="35" t="str">
+      <x:c r="A7" s="33" t="str">
         <x:v>Défini = spécification. Établi = référence documentée. Les colonnes d’adaptation restent des propositions.</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
@@ -2118,95 +2112,95 @@
       <x:c r="M8" s="2"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="30" t="str">
+      <x:c r="A9" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="29" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
+      <x:c r="C9" s="29" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="str">
+      <x:c r="D9" s="29" t="str">
         <x:v>Prototype</x:v>
       </x:c>
-      <x:c r="E9" s="31" t="str">
+      <x:c r="E9" s="29" t="str">
         <x:v>Intégré</x:v>
       </x:c>
-      <x:c r="F9" s="31" t="str">
+      <x:c r="F9" s="29" t="str">
         <x:v>Validé</x:v>
       </x:c>
-      <x:c r="G9" s="31" t="str">
+      <x:c r="G9" s="29" t="str">
         <x:v>Établi</x:v>
       </x:c>
-      <x:c r="H9" s="31" t="str">
+      <x:c r="H9" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="I9" s="31" t="str">
+      <x:c r="I9" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="str">
+      <x:c r="J9" s="29" t="str">
         <x:v>Coupé attesté</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="str">
+      <x:c r="K9" s="29" t="str">
         <x:v>Concept abandonné</x:v>
       </x:c>
-      <x:c r="L9" s="31" t="str">
+      <x:c r="L9" s="29" t="str">
         <x:v>Allégation écartée</x:v>
       </x:c>
-      <x:c r="M9" s="32" t="str">
+      <x:c r="M9" s="30" t="str">
         <x:v>Priorité P0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="36" t="str">
+      <x:c r="A10" s="34" t="str">
         <x:v>Personnages</x:v>
       </x:c>
-      <x:c r="B10" s="40" t="n">
+      <x:c r="B10" s="38" t="n">
         <x:f>COUNTA('Personnages'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C10" s="40" t="n">
+      <x:c r="C10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D10" s="40" t="n">
+      <x:c r="D10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="40" t="n">
+      <x:c r="E10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="40" t="n">
+      <x:c r="F10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="40" t="n">
+      <x:c r="G10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H10" s="40" t="n">
+      <x:c r="H10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I10" s="40" t="n">
+      <x:c r="I10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="40" t="n">
+      <x:c r="J10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="40" t="n">
+      <x:c r="K10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="40" t="n">
+      <x:c r="L10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="40" t="n">
+      <x:c r="M10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2215,104 +2209,104 @@
       <x:c r="A11" s="2" t="str">
         <x:v>PNJ</x:v>
       </x:c>
-      <x:c r="B11" s="41" t="n">
+      <x:c r="B11" s="39" t="n">
         <x:f>COUNTA('PNJ'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C11" s="41" t="n">
+      <x:c r="C11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D11" s="41" t="n">
+      <x:c r="D11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="41" t="n">
+      <x:c r="E11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="41" t="n">
+      <x:c r="F11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="41" t="n">
+      <x:c r="G11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Établi")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H11" s="41" t="n">
+      <x:c r="H11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I11" s="41" t="n">
+      <x:c r="I11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="41" t="n">
+      <x:c r="J11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="41" t="n">
+      <x:c r="K11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="41" t="n">
+      <x:c r="L11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="41" t="n">
+      <x:c r="M11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="36" t="str">
+      <x:c r="A12" s="34" t="str">
         <x:v>Espèces et factions</x:v>
       </x:c>
-      <x:c r="B12" s="40" t="n">
+      <x:c r="B12" s="38" t="n">
         <x:f>COUNTA('Especes_factions'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C12" s="40" t="n">
+      <x:c r="C12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$13,"Défini")</x:f>
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D12" s="40" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$13,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="40" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="40" t="n">
+      <x:c r="F12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="40" t="n">
+      <x:c r="G12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$13,"Établi")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H12" s="40" t="n">
+      <x:c r="H12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I12" s="40" t="n">
+      <x:c r="I12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="40" t="n">
+      <x:c r="J12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="40" t="n">
+      <x:c r="K12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="40" t="n">
+      <x:c r="L12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="40" t="n">
+      <x:c r="M12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2321,104 +2315,104 @@
       <x:c r="A13" s="2" t="str">
         <x:v>Mondes</x:v>
       </x:c>
-      <x:c r="B13" s="41" t="n">
+      <x:c r="B13" s="39" t="n">
         <x:f>COUNTA('Mondes'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C13" s="41" t="n">
+      <x:c r="C13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$8,"Défini")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="39" t="n">
+        <x:f>COUNTIFS('Mondes'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D13" s="41" t="n">
-        <x:f>COUNTIFS('Mondes'!$C$7:$C$8,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" s="41" t="n">
+      <x:c r="E13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="41" t="n">
+      <x:c r="F13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="41" t="n">
+      <x:c r="G13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H13" s="41" t="n">
+      <x:c r="H13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I13" s="41" t="n">
+      <x:c r="I13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J13" s="41" t="n">
+      <x:c r="J13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="41" t="n">
+      <x:c r="K13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="41" t="n">
+      <x:c r="L13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="41" t="n">
+      <x:c r="M13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="36" t="str">
+      <x:c r="A14" s="34" t="str">
         <x:v>Zones</x:v>
       </x:c>
-      <x:c r="B14" s="40" t="n">
+      <x:c r="B14" s="38" t="n">
         <x:f>COUNTA('Zones'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C14" s="40" t="n">
+      <x:c r="C14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D14" s="40" t="n">
+      <x:c r="D14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="40" t="n">
+      <x:c r="E14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="40" t="n">
+      <x:c r="F14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="40" t="n">
+      <x:c r="G14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H14" s="40" t="n">
+      <x:c r="H14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I14" s="40" t="n">
+      <x:c r="I14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J14" s="40" t="n">
+      <x:c r="J14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="40" t="n">
+      <x:c r="K14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="40" t="n">
+      <x:c r="L14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="40" t="n">
+      <x:c r="M14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2427,104 +2421,104 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Liaisons</x:v>
       </x:c>
-      <x:c r="B15" s="41" t="n">
+      <x:c r="B15" s="39" t="n">
         <x:f>COUNTA('Liaisons'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C15" s="41" t="n">
+      <x:c r="C15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D15" s="41" t="n">
+      <x:c r="D15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="41" t="n">
+      <x:c r="E15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="41" t="n">
+      <x:c r="F15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="41" t="n">
+      <x:c r="G15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H15" s="41" t="n">
+      <x:c r="H15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I15" s="41" t="n">
+      <x:c r="I15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J15" s="41" t="n">
+      <x:c r="J15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="41" t="n">
+      <x:c r="K15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="41" t="n">
+      <x:c r="L15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="41" t="n">
+      <x:c r="M15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="36" t="str">
+      <x:c r="A16" s="34" t="str">
         <x:v>Décors</x:v>
       </x:c>
-      <x:c r="B16" s="40" t="n">
+      <x:c r="B16" s="38" t="n">
         <x:f>COUNTA('Decors'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C16" s="40" t="n">
+      <x:c r="C16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D16" s="40" t="n">
+      <x:c r="D16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="40" t="n">
+      <x:c r="E16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="40" t="n">
+      <x:c r="F16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="40" t="n">
+      <x:c r="G16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="40" t="n">
+      <x:c r="H16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="40" t="n">
+      <x:c r="I16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J16" s="40" t="n">
+      <x:c r="J16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" s="40" t="n">
+      <x:c r="K16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="40" t="n">
+      <x:c r="L16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="40" t="n">
+      <x:c r="M16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2533,104 +2527,104 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Props</x:v>
       </x:c>
-      <x:c r="B17" s="41" t="n">
+      <x:c r="B17" s="39" t="n">
         <x:f>COUNTA('Props'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C17" s="41" t="n">
+      <x:c r="C17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D17" s="41" t="n">
+      <x:c r="D17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="41" t="n">
+      <x:c r="E17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="41" t="n">
+      <x:c r="F17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="41" t="n">
+      <x:c r="G17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H17" s="41" t="n">
+      <x:c r="H17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I17" s="41" t="n">
+      <x:c r="I17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J17" s="41" t="n">
+      <x:c r="J17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="41" t="n">
+      <x:c r="K17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="41" t="n">
+      <x:c r="L17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="41" t="n">
+      <x:c r="M17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="36" t="str">
+      <x:c r="A18" s="34" t="str">
         <x:v>Ennemis et boss</x:v>
       </x:c>
-      <x:c r="B18" s="40" t="n">
+      <x:c r="B18" s="38" t="n">
         <x:f>COUNTA('Ennemis_boss'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C18" s="40" t="n">
+      <x:c r="C18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D18" s="40" t="n">
+      <x:c r="D18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="40" t="n">
+      <x:c r="E18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="40" t="n">
+      <x:c r="F18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="40" t="n">
+      <x:c r="G18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H18" s="40" t="n">
+      <x:c r="H18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I18" s="40" t="n">
+      <x:c r="I18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J18" s="40" t="n">
+      <x:c r="J18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="40" t="n">
+      <x:c r="K18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="40" t="n">
+      <x:c r="L18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="40" t="n">
+      <x:c r="M18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2639,104 +2633,104 @@
       <x:c r="A19" s="2" t="str">
         <x:v>Missions</x:v>
       </x:c>
-      <x:c r="B19" s="41" t="n">
+      <x:c r="B19" s="39" t="n">
         <x:f>COUNTA('Missions'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C19" s="41" t="n">
+      <x:c r="C19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D19" s="41" t="n">
+      <x:c r="D19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E19" s="41" t="n">
+      <x:c r="E19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="41" t="n">
+      <x:c r="F19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="41" t="n">
+      <x:c r="G19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H19" s="41" t="n">
+      <x:c r="H19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I19" s="41" t="n">
+      <x:c r="I19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J19" s="41" t="n">
+      <x:c r="J19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="41" t="n">
+      <x:c r="K19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="41" t="n">
+      <x:c r="L19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M19" s="41" t="n">
+      <x:c r="M19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$E$7:$E$14,"P0")</x:f>
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="36" t="str">
+      <x:c r="A20" s="34" t="str">
         <x:v>Secondaires et DLC</x:v>
       </x:c>
-      <x:c r="B20" s="40" t="n">
+      <x:c r="B20" s="38" t="n">
         <x:f>COUNTA('Secondaires_DLC'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C20" s="40" t="n">
+      <x:c r="C20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D20" s="40" t="n">
+      <x:c r="D20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="40" t="n">
+      <x:c r="E20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="40" t="n">
+      <x:c r="F20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" s="40" t="n">
+      <x:c r="G20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H20" s="40" t="n">
+      <x:c r="H20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I20" s="40" t="n">
+      <x:c r="I20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J20" s="40" t="n">
+      <x:c r="J20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K20" s="40" t="n">
+      <x:c r="K20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="40" t="n">
+      <x:c r="L20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="40" t="n">
+      <x:c r="M20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2745,104 +2739,104 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Choix et relations</x:v>
       </x:c>
-      <x:c r="B21" s="41" t="n">
+      <x:c r="B21" s="39" t="n">
         <x:f>COUNTA('Choix_relations'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C21" s="41" t="n">
+      <x:c r="C21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D21" s="41" t="n">
+      <x:c r="D21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="41" t="n">
+      <x:c r="E21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="41" t="n">
+      <x:c r="F21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G21" s="41" t="n">
+      <x:c r="G21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H21" s="41" t="n">
+      <x:c r="H21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I21" s="41" t="n">
+      <x:c r="I21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J21" s="41" t="n">
+      <x:c r="J21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="41" t="n">
+      <x:c r="K21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="41" t="n">
+      <x:c r="L21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="41" t="n">
+      <x:c r="M21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="36" t="str">
+      <x:c r="A22" s="34" t="str">
         <x:v>Dialogues</x:v>
       </x:c>
-      <x:c r="B22" s="40" t="n">
+      <x:c r="B22" s="38" t="n">
         <x:f>COUNTA('Dialogues'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C22" s="40" t="n">
+      <x:c r="C22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D22" s="40" t="n">
+      <x:c r="D22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="40" t="n">
+      <x:c r="E22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F22" s="40" t="n">
+      <x:c r="F22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="40" t="n">
+      <x:c r="G22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="40" t="n">
+      <x:c r="H22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I22" s="40" t="n">
+      <x:c r="I22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J22" s="40" t="n">
+      <x:c r="J22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="40" t="n">
+      <x:c r="K22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="40" t="n">
+      <x:c r="L22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="40" t="n">
+      <x:c r="M22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2851,104 +2845,104 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Cinématiques</x:v>
       </x:c>
-      <x:c r="B23" s="41" t="n">
+      <x:c r="B23" s="39" t="n">
         <x:f>COUNTA('Cinematiques'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C23" s="41" t="n">
+      <x:c r="C23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D23" s="41" t="n">
+      <x:c r="D23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="41" t="n">
+      <x:c r="E23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F23" s="41" t="n">
+      <x:c r="F23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="41" t="n">
+      <x:c r="G23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H23" s="41" t="n">
+      <x:c r="H23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I23" s="41" t="n">
+      <x:c r="I23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J23" s="41" t="n">
+      <x:c r="J23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K23" s="41" t="n">
+      <x:c r="K23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="41" t="n">
+      <x:c r="L23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="41" t="n">
+      <x:c r="M23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="36" t="str">
+      <x:c r="A24" s="34" t="str">
         <x:v>Armes</x:v>
       </x:c>
-      <x:c r="B24" s="40" t="n">
+      <x:c r="B24" s="38" t="n">
         <x:f>COUNTA('Armes'!$A$7:$A$7)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C24" s="40" t="n">
+      <x:c r="C24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Défini")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D24" s="40" t="n">
+      <x:c r="D24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E24" s="40" t="n">
+      <x:c r="E24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F24" s="40" t="n">
+      <x:c r="F24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="40" t="n">
+      <x:c r="G24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H24" s="40" t="n">
+      <x:c r="H24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I24" s="40" t="n">
+      <x:c r="I24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J24" s="40" t="n">
+      <x:c r="J24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="40" t="n">
+      <x:c r="K24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="40" t="n">
+      <x:c r="L24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="40" t="n">
+      <x:c r="M24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2957,104 +2951,104 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Armures et équipement</x:v>
       </x:c>
-      <x:c r="B25" s="41" t="n">
+      <x:c r="B25" s="39" t="n">
         <x:f>COUNTA('Armures_equipement'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C25" s="41" t="n">
+      <x:c r="C25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D25" s="41" t="n">
+      <x:c r="D25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E25" s="41" t="n">
+      <x:c r="E25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F25" s="41" t="n">
+      <x:c r="F25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G25" s="41" t="n">
+      <x:c r="G25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H25" s="41" t="n">
+      <x:c r="H25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I25" s="41" t="n">
+      <x:c r="I25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J25" s="41" t="n">
+      <x:c r="J25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K25" s="41" t="n">
+      <x:c r="K25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="41" t="n">
+      <x:c r="L25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="41" t="n">
+      <x:c r="M25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="36" t="str">
+      <x:c r="A26" s="34" t="str">
         <x:v>Pouvoirs</x:v>
       </x:c>
-      <x:c r="B26" s="40" t="n">
+      <x:c r="B26" s="38" t="n">
         <x:f>COUNTA('Pouvoirs'!$A$7:$A$7)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C26" s="40" t="n">
+      <x:c r="C26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Défini")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D26" s="40" t="n">
+      <x:c r="D26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E26" s="40" t="n">
+      <x:c r="E26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F26" s="40" t="n">
+      <x:c r="F26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="40" t="n">
+      <x:c r="G26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H26" s="40" t="n">
+      <x:c r="H26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I26" s="40" t="n">
+      <x:c r="I26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J26" s="40" t="n">
+      <x:c r="J26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="40" t="n">
+      <x:c r="K26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="40" t="n">
+      <x:c r="L26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="40" t="n">
+      <x:c r="M26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3063,104 +3057,104 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Movesets alliés</x:v>
       </x:c>
-      <x:c r="B27" s="41" t="n">
+      <x:c r="B27" s="39" t="n">
         <x:f>COUNTA('Movesets_allies'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C27" s="41" t="n">
+      <x:c r="C27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D27" s="41" t="n">
+      <x:c r="D27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E27" s="41" t="n">
+      <x:c r="E27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F27" s="41" t="n">
+      <x:c r="F27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="41" t="n">
+      <x:c r="G27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="41" t="n">
+      <x:c r="H27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I27" s="41" t="n">
+      <x:c r="I27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J27" s="41" t="n">
+      <x:c r="J27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="41" t="n">
+      <x:c r="K27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="41" t="n">
+      <x:c r="L27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="41" t="n">
+      <x:c r="M27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="36" t="str">
+      <x:c r="A28" s="34" t="str">
         <x:v>Movesets ennemis</x:v>
       </x:c>
-      <x:c r="B28" s="40" t="n">
+      <x:c r="B28" s="38" t="n">
         <x:f>COUNTA('Movesets_ennemis'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C28" s="40" t="n">
+      <x:c r="C28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D28" s="40" t="n">
+      <x:c r="D28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E28" s="40" t="n">
+      <x:c r="E28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="40" t="n">
+      <x:c r="F28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="40" t="n">
+      <x:c r="G28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="40" t="n">
+      <x:c r="H28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I28" s="40" t="n">
+      <x:c r="I28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J28" s="40" t="n">
+      <x:c r="J28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="40" t="n">
+      <x:c r="K28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="40" t="n">
+      <x:c r="L28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="40" t="n">
+      <x:c r="M28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3169,104 +3163,104 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Animations</x:v>
       </x:c>
-      <x:c r="B29" s="41" t="n">
+      <x:c r="B29" s="39" t="n">
         <x:f>COUNTA('Animations'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C29" s="41" t="n">
+      <x:c r="C29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D29" s="41" t="n">
+      <x:c r="D29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E29" s="41" t="n">
+      <x:c r="E29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="41" t="n">
+      <x:c r="F29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="41" t="n">
+      <x:c r="G29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="41" t="n">
+      <x:c r="H29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I29" s="41" t="n">
+      <x:c r="I29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J29" s="41" t="n">
+      <x:c r="J29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="41" t="n">
+      <x:c r="K29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="41" t="n">
+      <x:c r="L29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="41" t="n">
+      <x:c r="M29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="36" t="str">
+      <x:c r="A30" s="34" t="str">
         <x:v>Sprites</x:v>
       </x:c>
-      <x:c r="B30" s="40" t="n">
+      <x:c r="B30" s="38" t="n">
         <x:f>COUNTA('Sprites'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C30" s="40" t="n">
+      <x:c r="C30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D30" s="40" t="n">
+      <x:c r="D30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E30" s="40" t="n">
+      <x:c r="E30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F30" s="40" t="n">
+      <x:c r="F30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="40" t="n">
+      <x:c r="G30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="40" t="n">
+      <x:c r="H30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I30" s="40" t="n">
+      <x:c r="I30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J30" s="40" t="n">
+      <x:c r="J30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="40" t="n">
+      <x:c r="K30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="40" t="n">
+      <x:c r="L30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M30" s="40" t="n">
+      <x:c r="M30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3275,104 +3269,104 @@
       <x:c r="A31" s="2" t="str">
         <x:v>VFX</x:v>
       </x:c>
-      <x:c r="B31" s="41" t="n">
+      <x:c r="B31" s="39" t="n">
         <x:f>COUNTA('VFX'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C31" s="41" t="n">
+      <x:c r="C31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D31" s="41" t="n">
+      <x:c r="D31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="41" t="n">
+      <x:c r="E31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F31" s="41" t="n">
+      <x:c r="F31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G31" s="41" t="n">
+      <x:c r="G31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H31" s="41" t="n">
+      <x:c r="H31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I31" s="41" t="n">
+      <x:c r="I31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J31" s="41" t="n">
+      <x:c r="J31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="41" t="n">
+      <x:c r="K31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L31" s="41" t="n">
+      <x:c r="L31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M31" s="41" t="n">
+      <x:c r="M31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="36" t="str">
+      <x:c r="A32" s="34" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="B32" s="40" t="n">
+      <x:c r="B32" s="38" t="n">
         <x:f>COUNTA('Audio'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C32" s="40" t="n">
+      <x:c r="C32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D32" s="40" t="n">
+      <x:c r="D32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E32" s="40" t="n">
+      <x:c r="E32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F32" s="40" t="n">
+      <x:c r="F32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="40" t="n">
+      <x:c r="G32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="40" t="n">
+      <x:c r="H32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I32" s="40" t="n">
+      <x:c r="I32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J32" s="40" t="n">
+      <x:c r="J32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="40" t="n">
+      <x:c r="K32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L32" s="40" t="n">
+      <x:c r="L32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="40" t="n">
+      <x:c r="M32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$E$7:$E$11,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3381,104 +3375,104 @@
       <x:c r="A33" s="2" t="str">
         <x:v>Systèmes et UI</x:v>
       </x:c>
-      <x:c r="B33" s="41" t="n">
+      <x:c r="B33" s="39" t="n">
         <x:f>COUNTA('UI_systemes'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C33" s="41" t="n">
+      <x:c r="C33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D33" s="41" t="n">
+      <x:c r="D33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E33" s="41" t="n">
+      <x:c r="E33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F33" s="41" t="n">
+      <x:c r="F33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G33" s="41" t="n">
+      <x:c r="G33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H33" s="41" t="n">
+      <x:c r="H33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="41" t="n">
+      <x:c r="I33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J33" s="41" t="n">
+      <x:c r="J33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="41" t="n">
+      <x:c r="K33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L33" s="41" t="n">
+      <x:c r="L33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="41" t="n">
+      <x:c r="M33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$E$7:$E$14,"P0")</x:f>
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="36" t="str">
+      <x:c r="A34" s="34" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="B34" s="40" t="n">
+      <x:c r="B34" s="38" t="n">
         <x:f>COUNTA('QA'!$A$7:$A$18)</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C34" s="40" t="n">
+      <x:c r="C34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Défini")</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D34" s="40" t="n">
+      <x:c r="D34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E34" s="40" t="n">
+      <x:c r="E34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F34" s="40" t="n">
+      <x:c r="F34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="40" t="n">
+      <x:c r="G34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="40" t="n">
+      <x:c r="H34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I34" s="40" t="n">
+      <x:c r="I34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Extrapolation")</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J34" s="40" t="n">
+      <x:c r="J34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K34" s="40" t="n">
+      <x:c r="K34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L34" s="40" t="n">
+      <x:c r="L34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M34" s="40" t="n">
+      <x:c r="M34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$E$7:$E$18,"P0")</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -3487,119 +3481,119 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Continuité</x:v>
       </x:c>
-      <x:c r="B35" s="41" t="n">
+      <x:c r="B35" s="39" t="n">
         <x:f>COUNTA('Continuite'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C35" s="41" t="n">
+      <x:c r="C35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D35" s="41" t="n">
+      <x:c r="D35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E35" s="41" t="n">
+      <x:c r="E35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F35" s="41" t="n">
+      <x:c r="F35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G35" s="41" t="n">
+      <x:c r="G35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$14,"Établi")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H35" s="41" t="n">
+      <x:c r="H35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I35" s="41" t="n">
+      <x:c r="I35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J35" s="41" t="n">
+      <x:c r="J35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K35" s="41" t="n">
+      <x:c r="K35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L35" s="41" t="n">
+      <x:c r="L35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="41" t="n">
+      <x:c r="M35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$E$7:$E$14,"P0")</x:f>
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="2"/>
-      <x:c r="B36" s="41"/>
-      <x:c r="C36" s="41"/>
-      <x:c r="D36" s="41"/>
-      <x:c r="E36" s="41"/>
-      <x:c r="F36" s="41"/>
-      <x:c r="G36" s="41"/>
-      <x:c r="H36" s="41"/>
-      <x:c r="I36" s="41"/>
-      <x:c r="J36" s="41"/>
-      <x:c r="K36" s="41"/>
-      <x:c r="L36" s="41"/>
-      <x:c r="M36" s="41"/>
+      <x:c r="B36" s="39"/>
+      <x:c r="C36" s="39"/>
+      <x:c r="D36" s="39"/>
+      <x:c r="E36" s="39"/>
+      <x:c r="F36" s="39"/>
+      <x:c r="G36" s="39"/>
+      <x:c r="H36" s="39"/>
+      <x:c r="I36" s="39"/>
+      <x:c r="J36" s="39"/>
+      <x:c r="K36" s="39"/>
+      <x:c r="L36" s="39"/>
+      <x:c r="M36" s="39"/>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="23" t="str">
+      <x:c r="A37" s="21" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B37" s="42" t="n">
+      <x:c r="B37" s="40" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>159</x:v>
       </x:c>
-      <x:c r="C37" s="42" t="n">
+      <x:c r="C37" s="40" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="D37" s="42" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D37" s="40" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="42" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E37" s="40" t="n">
         <x:f>SUM(E10:E35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F37" s="42" t="n">
+      <x:c r="F37" s="40" t="n">
         <x:f>SUM(F10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G37" s="42" t="n">
+      <x:c r="G37" s="40" t="n">
         <x:f>SUM(G10:G35)</x:f>
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H37" s="42" t="n">
+      <x:c r="H37" s="40" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I37" s="42" t="n">
+      <x:c r="I37" s="40" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>131</x:v>
       </x:c>
-      <x:c r="J37" s="42" t="n">
+      <x:c r="J37" s="40" t="n">
         <x:f>SUM(J10:J35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="42" t="n">
+      <x:c r="K37" s="40" t="n">
         <x:f>SUM(K10:K35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L37" s="42" t="n">
+      <x:c r="L37" s="40" t="n">
         <x:f>SUM(L10:L35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M37" s="42" t="n">
+      <x:c r="M37" s="40" t="n">
         <x:f>SUM(M10:M35)</x:f>
         <x:v>21</x:v>
       </x:c>
@@ -3823,61 +3817,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -3927,8 +3921,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -3978,8 +3972,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4029,8 +4023,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4080,8 +4074,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4117,7 +4111,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc99f20486a83482d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3cbc14cbf4154761"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4257,61 +4251,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4363,8 +4357,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -4414,8 +4408,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -4465,8 +4459,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -4516,8 +4510,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -4567,8 +4561,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -4618,8 +4612,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -4669,8 +4663,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -4720,8 +4714,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -4755,7 +4749,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R626bd696153d4776"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc7d2240f1194642"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4895,61 +4889,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5001,8 +4995,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5052,8 +5046,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5103,8 +5097,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5154,8 +5148,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5205,8 +5199,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -5256,8 +5250,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -5307,8 +5301,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -5358,8 +5352,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -5393,7 +5387,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R034256e1fdfb4708"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8ebf050cc0945c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5533,61 +5527,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5639,8 +5633,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5690,8 +5684,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5741,8 +5735,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5792,8 +5786,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5843,8 +5837,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -5894,8 +5888,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -5945,8 +5939,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -5996,8 +5990,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -6031,7 +6025,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11a4c2b85890476a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fe7876c09df4c52"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6171,61 +6165,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6277,8 +6271,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6330,8 +6324,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6383,8 +6377,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6436,8 +6430,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6489,8 +6483,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6542,8 +6536,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6595,8 +6589,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6648,8 +6642,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6701,8 +6695,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6754,8 +6748,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str">
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6791,7 +6785,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ee3a9e98df44ac9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51b9eb5f89a14788"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6931,61 +6925,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7037,8 +7031,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -7088,8 +7082,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -7139,8 +7133,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -7190,8 +7184,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -7241,8 +7235,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -7292,8 +7286,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -7343,8 +7337,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -7394,8 +7388,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -7429,7 +7423,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78a914fde1904e68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4f0569066674d43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7569,74 +7563,74 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
       <x:c r="A7" s="2"/>
-      <x:c r="B7" s="33" t="str">
+      <x:c r="B7" s="31" t="str">
         <x:v>Aucun élément inventorié. Voir les limites dans Guide.</x:v>
       </x:c>
-      <x:c r="C7" s="33"/>
-      <x:c r="D7" s="33"/>
-      <x:c r="E7" s="33"/>
-      <x:c r="F7" s="33"/>
-      <x:c r="G7" s="33"/>
+      <x:c r="C7" s="31"/>
+      <x:c r="D7" s="31"/>
+      <x:c r="E7" s="31"/>
+      <x:c r="F7" s="31"/>
+      <x:c r="G7" s="31"/>
       <x:c r="H7" s="2"/>
       <x:c r="I7" s="2"/>
       <x:c r="J7" s="2"/>
@@ -7790,61 +7784,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7890,10 +7884,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>NEX-SRC-MORDA</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Nakmor_Morda</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -7929,7 +7923,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b5495a25c5d4dc0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d141fecd4ad4301"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8069,74 +8063,74 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
       <x:c r="A7" s="2"/>
-      <x:c r="B7" s="33" t="str">
+      <x:c r="B7" s="31" t="str">
         <x:v>Aucun élément inventorié. Voir les limites dans Guide.</x:v>
       </x:c>
-      <x:c r="C7" s="33"/>
-      <x:c r="D7" s="33"/>
-      <x:c r="E7" s="33"/>
-      <x:c r="F7" s="33"/>
-      <x:c r="G7" s="33"/>
+      <x:c r="C7" s="31"/>
+      <x:c r="D7" s="31"/>
+      <x:c r="E7" s="31"/>
+      <x:c r="F7" s="31"/>
+      <x:c r="G7" s="31"/>
       <x:c r="H7" s="2"/>
       <x:c r="I7" s="2"/>
       <x:c r="J7" s="2"/>
@@ -8290,61 +8284,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8394,8 +8388,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8443,8 +8437,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -8492,8 +8486,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -8541,8 +8535,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -8590,8 +8584,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -8639,8 +8633,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -8674,7 +8668,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdba14db271be4789"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1373c149cd24406d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8814,61 +8808,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8914,10 +8908,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>NEX-SRC-AUTHOR</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.jasonhough.com/book/mass-effect</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -8963,10 +8957,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>NEX-SRC-KESH</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Nakmor_Kesh</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9012,10 +9006,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>NEX-SRC-KANDROS</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Tiran_Kandros</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9051,7 +9045,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca23d744ca114748"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67fde3f7b10a4c50"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9191,61 +9185,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9297,8 +9291,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9348,8 +9342,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -9399,8 +9393,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -9450,8 +9444,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -9485,7 +9479,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb717d0f5eee04b28"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48ce12e1564f4353"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9625,61 +9619,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9731,8 +9725,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9782,8 +9776,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -9833,8 +9827,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -9884,8 +9878,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -9935,8 +9929,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -9986,8 +9980,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -10037,8 +10031,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -10088,8 +10082,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -10139,8 +10133,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -10190,8 +10184,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D16">
@@ -10225,7 +10219,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfde2f7732e85403b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b46fbbdc8354758"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10365,61 +10359,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10471,8 +10465,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10522,8 +10516,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10573,8 +10567,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10624,8 +10618,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10675,8 +10669,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -10726,8 +10720,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -10777,8 +10771,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -10828,8 +10822,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -10879,8 +10873,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -10930,8 +10924,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D16">
@@ -10965,7 +10959,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e71caf3553849f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf6b9de9e4ea43ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11105,61 +11099,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11211,8 +11205,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11262,8 +11256,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11313,8 +11307,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11364,8 +11358,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -11399,7 +11393,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45d5703a8bca4389"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb1bab55909346df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11539,61 +11533,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11643,8 +11637,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11692,8 +11686,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11741,8 +11735,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11790,8 +11784,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -11839,8 +11833,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D11">
@@ -11874,7 +11868,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re71bb565bcec4ec0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c22aa112a1a4114"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12014,61 +12008,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12118,8 +12112,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12167,8 +12161,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12216,8 +12210,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12265,8 +12259,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12314,8 +12308,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="44" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -12363,8 +12357,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -12412,8 +12406,8 @@
       <x:c r="O13" s="9" t="str"/>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -12461,8 +12455,8 @@
       <x:c r="O14" s="7" t="str"/>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -12496,7 +12490,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe19e2bc9b014875"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc39204850192433a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12636,61 +12630,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12742,8 +12736,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12793,8 +12787,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12844,8 +12838,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12895,8 +12889,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12946,8 +12940,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -12997,8 +12991,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -13048,8 +13042,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -13099,8 +13093,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="82" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -13142,8 +13136,8 @@
       <x:c r="O15" s="9" t="str"/>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="82" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -13185,8 +13179,8 @@
       <x:c r="O16" s="7" t="str"/>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -13228,8 +13222,8 @@
       <x:c r="O17" s="9" t="str"/>
       <x:c r="P17" s="9" t="str"/>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -13271,8 +13265,8 @@
       <x:c r="O18" s="7" t="str"/>
       <x:c r="P18" s="7" t="str"/>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D18">
@@ -13306,7 +13300,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R891d637f44b14afb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6da70f5fe49441f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13446,61 +13440,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13546,10 +13540,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>NEX-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Andromeda:_Nexus_Uprising</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -13593,8 +13587,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -13640,10 +13634,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>NEX-SRC-CODEX</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Codex_%28Mass_Effect%3A_Andromeda%29/The_Andromeda_Initiative</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -13689,10 +13683,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>NEX-SRC-SLOANE</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Sloane_Kelly</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -13738,10 +13732,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>NEX-SRC-MORDA</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Nakmor_Morda</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -13787,10 +13781,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>NEX-SRC-KESH</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Nakmor_Kesh</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -13834,8 +13828,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -13879,8 +13873,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -13916,7 +13910,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfda0bd64f3194b30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70e9f7a177bb49ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13981,10 +13975,10 @@
       <x:c r="F5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Champ</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="30" t="str">
         <x:v>Définition</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
@@ -14033,7 +14027,7 @@
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Direction du Nexus, ingénieurs, personnel réveillé et mutinerie ; adaptation originale centrée sur maintien des services, circulation de l’information et protection civile.</x:v>
+        <x:v>159 fiches de production ; 5 fiches au stade Prototype de portée partielle. Les autres livrables restent des spécifications ; aucun achèvement intégral 1:1 revendiqué.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -14052,11 +14046,11 @@
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
-      <x:c r="B12" s="45" t="d">
+      <x:c r="B12" s="43" t="d">
         <x:v>2026-10-22T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
@@ -14209,22 +14203,22 @@
       <x:c r="F25" s="2"/>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="30" t="str">
+      <x:c r="A26" s="28" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="29" t="str">
         <x:v>Titre</x:v>
       </x:c>
-      <x:c r="C26" s="31" t="str">
+      <x:c r="C26" s="29" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="str">
+      <x:c r="D26" s="29" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E26" s="31" t="str">
+      <x:c r="E26" s="29" t="str">
         <x:v>Périmètre</x:v>
       </x:c>
-      <x:c r="F26" s="32" t="str">
+      <x:c r="F26" s="30" t="str">
         <x:v>Accès et limites</x:v>
       </x:c>
     </x:row>
@@ -14513,13 +14507,13 @@
       <x:c r="F42" s="2"/>
     </x:row>
     <x:row r="43" ht="34" customHeight="1">
-      <x:c r="A43" s="30" t="str">
+      <x:c r="A43" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B43" s="31" t="str">
+      <x:c r="B43" s="29" t="str">
         <x:v>Couverture actuelle</x:v>
       </x:c>
-      <x:c r="C43" s="32" t="str">
+      <x:c r="C43" s="30" t="str">
         <x:v>Travail restant</x:v>
       </x:c>
       <x:c r="D43" s="2"/>
@@ -14610,10 +14604,16 @@
       <x:c r="E49" s="2"/>
       <x:c r="F49" s="2"/>
     </x:row>
-    <x:row r="50" ht="22" customHeight="1">
-      <x:c r="A50" s="2"/>
-      <x:c r="B50" s="2"/>
-      <x:c r="C50" s="2"/>
+    <x:row r="50" ht="96" customHeight="1">
+      <x:c r="A50" s="6" t="str">
+        <x:v>Complément pouvoirs, modules et lectures</x:v>
+      </x:c>
+      <x:c r="B50" s="6" t="str">
+        <x:v>0 fiches de pouvoirs utilisées, 0 familles de modules préparables et 5 références consultables dans une lecture documentaire. Les chemins et preuves sont inscrits sur les seules lignes Prototype.</x:v>
+      </x:c>
+      <x:c r="C50" s="6" t="str">
+        <x:v>Arbres et progression complets, modèles et rangs exacts, campagnes et dialogues intégraux, niveaux et ressources visuelles propres à l’œuvre restent à réaliser ou vérifier. Les références lues ne rendent pas leurs personnages jouables.</x:v>
+      </x:c>
       <x:c r="D50" s="2"/>
       <x:c r="E50" s="2"/>
       <x:c r="F50" s="2"/>
@@ -15169,6 +15169,14 @@
       <x:c r="D119" s="2"/>
       <x:c r="E119" s="2"/>
       <x:c r="F119" s="2"/>
+    </x:row>
+    <x:row r="120" ht="22" customHeight="1">
+      <x:c r="A120" s="2"/>
+      <x:c r="B120" s="2"/>
+      <x:c r="C120" s="2"/>
+      <x:c r="D120" s="2"/>
+      <x:c r="E120" s="2"/>
+      <x:c r="F120" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15310,61 +15318,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15410,10 +15418,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>NEX-SRC-TANN</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Jarun_Tann</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15459,10 +15467,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>NEX-SRC-EXILES</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Exiles</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15508,10 +15516,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>NEX-SRC-CALIX</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Calix_Corvannis</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15557,10 +15565,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>NEX-SRC-IRIDA</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Irida_Fadeer</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15606,10 +15614,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>NEX-SRC-MORDA</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Nakmor_Morda</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15655,10 +15663,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>NEX-SRC-MORDA</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Nakmor_Morda</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15704,10 +15712,10 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>NEX-SRC-GARSON</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Jien_Garson</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="S13" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15743,7 +15751,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2c883093ea947b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb618294f9d464f07"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15770,7 +15778,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="88" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -15883,61 +15891,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15949,7 +15957,7 @@
         <x:v>Initiative Andromède</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -15968,7 +15976,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Codex ref.nex.initiative ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire NEX-REF-INITIATIVE consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Préserver la crise précédant Mass Effect Andromeda : les choix locaux ne suppriment ni la révolte ni l’exil de Sloane et des autres personnes concernées. Ne pas résoudre dans ce module les mystères révélés plus tard par Ryder.</x:v>
@@ -15983,11 +15991,11 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>NEX-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://titanbooks.com/8747-mass-effect-nexus-uprising/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S7" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
@@ -16032,10 +16040,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>NEX-SRC-AUTHOR</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://www.jasonhough.com/book/mass-effect</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -16081,10 +16089,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>NEX-SRC-AUTHOR</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://www.jasonhough.com/book/mass-effect</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -16130,10 +16138,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>NEX-SRC-AUTHOR</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://www.jasonhough.com/book/mass-effect</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -16179,10 +16187,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>NEX-SRC-AUTHOR</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://www.jasonhough.com/book/mass-effect</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -16194,7 +16202,7 @@
         <x:v>Clan Nakmor</x:v>
       </x:c>
       <x:c r="C12" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D12" s="17" t="str">
         <x:v>Établi</x:v>
@@ -16213,7 +16221,7 @@
       <x:c r="J12" s="7" t="str"/>
       <x:c r="K12" s="7" t="str"/>
       <x:c r="L12" s="7" t="str">
-        <x:v>Codex ref.nex.nakmor ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire NEX-REF-NAKMOR consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M12" s="7" t="str">
         <x:v>Préserver la crise précédant Mass Effect Andromeda : les choix locaux ne suppriment ni la révolte ni l’exil de Sloane et des autres personnes concernées. Ne pas résoudre dans ce module les mystères révélés plus tard par Ryder.</x:v>
@@ -16228,11 +16236,11 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>NEX-SRC-MORDA</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Nakmor_Morda</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S12" s="7" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="82" customHeight="1">
@@ -16243,7 +16251,7 @@
         <x:v>Fléau</x:v>
       </x:c>
       <x:c r="C13" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D13" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16262,7 +16270,7 @@
       <x:c r="J13" s="9" t="str"/>
       <x:c r="K13" s="9" t="str"/>
       <x:c r="L13" s="9" t="str">
-        <x:v>Codex ref.nex.scourge ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire NEX-REF-SCOURGE consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M13" s="9" t="str">
         <x:v>Préserver la crise précédant Mass Effect Andromeda : les choix locaux ne suppriment ni la révolte ni l’exil de Sloane et des autres personnes concernées. Ne pas résoudre dans ce module les mystères révélés plus tard par Ryder.</x:v>
@@ -16277,11 +16285,11 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>NEX-SRC-CODEX</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Codex_%28Mass_Effect%3A_Andromeda%29/The_Andromeda_Initiative</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S13" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16316,7 +16324,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65e47533db4d4514"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf43ca99ef60b4630"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16343,7 +16351,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="69" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -16456,61 +16464,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16522,7 +16530,7 @@
         <x:v>Nexus</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16541,7 +16549,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Codex ref.nex.nexus ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire NEX-REF-NEXUS consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Préserver la crise précédant Mass Effect Andromeda : les choix locaux ne suppriment ni la révolte ni l’exil de Sloane et des autres personnes concernées. Ne pas résoudre dans ce module les mystères révélés plus tard par Ryder.</x:v>
@@ -16556,11 +16564,11 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>NEX-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Andromeda:_Nexus_Uprising</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S7" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
@@ -16571,7 +16579,7 @@
         <x:v>Amas Héléus</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
         <x:v>Établi</x:v>
@@ -16590,7 +16598,7 @@
       <x:c r="J8" s="7" t="str"/>
       <x:c r="K8" s="7" t="str"/>
       <x:c r="L8" s="7" t="str">
-        <x:v>Codex ref.nex.heleus ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire NEX-REF-HELEUS consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M8" s="7" t="str">
         <x:v>Préserver la crise précédant Mass Effect Andromeda : les choix locaux ne suppriment ni la révolte ni l’exil de Sloane et des autres personnes concernées. Ne pas résoudre dans ce module les mystères révélés plus tard par Ryder.</x:v>
@@ -16605,11 +16613,11 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>NEX-SRC-TANN</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Jarun_Tann</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S8" s="7" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16644,7 +16652,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2454745e947b4148"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a73074c86af46f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16784,61 +16792,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16888,8 +16896,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -16939,8 +16947,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -16990,8 +16998,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17041,8 +17049,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17092,8 +17100,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17143,8 +17151,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17194,8 +17202,8 @@
       <x:c r="O13" s="9" t="str"/>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17245,8 +17253,8 @@
       <x:c r="O14" s="7" t="str"/>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17282,7 +17290,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8331c7f680e941a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e058dc7ce1241b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17422,61 +17430,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -17528,8 +17536,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17581,8 +17589,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17634,8 +17642,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17687,8 +17695,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17740,8 +17748,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17793,8 +17801,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17846,8 +17854,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17899,8 +17907,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17936,7 +17944,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf81243f451c34751"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5478c0927664f30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18076,61 +18084,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18182,8 +18190,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -18233,8 +18241,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -18284,8 +18292,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -18335,8 +18343,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -18386,8 +18394,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -18437,8 +18445,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -18488,8 +18496,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -18539,8 +18547,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -18574,7 +18582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7efe595addbd4e35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc032861bada842f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18714,61 +18722,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18814,10 +18822,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>NEX-SRC-CODEX</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Codex_%28Mass_Effect%3A_Andromeda%29/The_Andromeda_Initiative</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -18863,10 +18871,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>NEX-SRC-IRIDA</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Irida_Fadeer</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -18902,7 +18910,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e50e2164e4349b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R161753c6bf694e4b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Nexus_Uprising_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Nexus_Uprising_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rfda1c2f5f8af486b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rfc4673e34a0f4e66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Ra68be84f58744001"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R566babc1bd274ddd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rcefb50e6f5bd4d9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rde261e969ce04590"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rfff6819604094b99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Ref062ccb16774ee2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R42fc06e86e964638"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R17cf87c44d054641"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rd18ecf30c04745f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R5696c6d7064b4298"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Ra2f262663a0b46c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R2dade13e15ab45cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R20d40c54772540e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R1f2f0a9460f94edf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rf61a0c18aaff4794"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R00dc3e428e8947c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R6bb878db564f4f06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R2eec4a5a679c4593"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R628692150d2f42a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R41273ec6ed914ca9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rce3b9d3d9ef44769"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R2e4849eb1d224a3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R8dd261115cff4449"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R06b0d75292844b74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R0c1e8bc6b25f45b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R66c3b6573e554183"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Re11d5afdc6fc4381"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R74b867398f634fbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R4c26581d04e14ec6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rf349e962d06d4a0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R936eb4c7746c453b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R29a70b9e1fa74238"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R44fba8fc608348a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rc16334ed59f342f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rfb86f154b94d4025"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R7e82781d6e01499d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R4784f657602344c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R74039fb77972459d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rd2ed4db82d604b33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R72d09fed721e4297"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R8f5ddba90a8c4056"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R2af279962a884dc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R62417105ebad41bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rcfba8f5b42ca426b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R89002ec03a784b3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rcf39ae28920c48f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R92981f083fd44ddb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R8fc764c3d6574538"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R7397cf7c5fea49e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rac576e71212e4b8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R66bbd5a19c244d0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rfed6f4ed02fc46de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R00c3abcc3f384fd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R60f8f08472c449c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4111,7 +4111,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3cbc14cbf4154761"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8613e8ad7e024dbd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4749,7 +4749,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc7d2240f1194642"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bedf40353424def"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5387,7 +5387,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8ebf050cc0945c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77c53bfec319469b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6025,7 +6025,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fe7876c09df4c52"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdfc00e098f74361"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6785,7 +6785,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51b9eb5f89a14788"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf5999a38b784cdc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7423,7 +7423,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4f0569066674d43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red7553c0f15143d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7923,7 +7923,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d141fecd4ad4301"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2ee6aa86f734c8c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8668,7 +8668,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1373c149cd24406d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64b9763b03824e6b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9045,7 +9045,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67fde3f7b10a4c50"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7a1a5de6b3e4d65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9479,7 +9479,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48ce12e1564f4353"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R916cecef787c4c1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10219,7 +10219,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b46fbbdc8354758"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8656441f7b55401c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10959,7 +10959,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf6b9de9e4ea43ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf1a8dfa30294e31"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11393,7 +11393,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb1bab55909346df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94f6d0e29ef3458a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11868,7 +11868,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c22aa112a1a4114"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9b7f1dbff2b40fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12490,7 +12490,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc39204850192433a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38aa7a7709a94f30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13300,7 +13300,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6da70f5fe49441f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7abddd7160984d1d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13910,7 +13910,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70e9f7a177bb49ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R518bb4ae1d73479f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15751,7 +15751,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb618294f9d464f07"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc860b6dd7904b86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16324,7 +16324,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf43ca99ef60b4630"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25b4c2b450df4958"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16652,7 +16652,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a73074c86af46f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1bce6e089d449f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17290,7 +17290,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e058dc7ce1241b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e2c6b1c7d884ce2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17944,7 +17944,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5478c0927664f30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8484f9d8b55b46b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18582,7 +18582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc032861bada842f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69c66ee0769745e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18910,7 +18910,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R161753c6bf694e4b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fbc8b9e6d14444e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Nexus_Uprising_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Nexus_Uprising_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Re11d5afdc6fc4381"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R74b867398f634fbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R4c26581d04e14ec6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rf349e962d06d4a0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R936eb4c7746c453b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R29a70b9e1fa74238"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R44fba8fc608348a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rc16334ed59f342f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rfb86f154b94d4025"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R7e82781d6e01499d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R4784f657602344c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R74039fb77972459d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rd2ed4db82d604b33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R72d09fed721e4297"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R8f5ddba90a8c4056"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R2af279962a884dc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R62417105ebad41bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rcfba8f5b42ca426b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R89002ec03a784b3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rcf39ae28920c48f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R92981f083fd44ddb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R8fc764c3d6574538"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R7397cf7c5fea49e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rac576e71212e4b8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R66bbd5a19c244d0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rfed6f4ed02fc46de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R00c3abcc3f384fd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R60f8f08472c449c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rca6beac03e954368"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R9a5f83ff1f604481"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R23df76bee67046b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R9c490112f33c4316"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rf68d7ce13cf545af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R665f2e646aa743b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R9101bc19f2384039"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rc28c2b4112bc4c00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R9b3d768eba1b4f6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R247f5f65195b48a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R379f7a0eea3e4b02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R4c7c1c6ff71e46d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R9466befa05584c52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R2f018f5163044feb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rd897ec71175e4ccf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R765a912e9c4c4253"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rb23c383404a447b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rf0d0f149f5b34161"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rb7219bfb47a44614"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R00a72dd1d3c44628"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Ra15bb6c08f0a4654"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R53cd2c5a3b1240d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rdcbcf5d380b24816"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R03dbbb1b1c8f4e4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R1a25efb6219742cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R02153bf8a20f43d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R1102aed2ba624790"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rd7e5b0d8cf7d4737"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4111,7 +4111,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8613e8ad7e024dbd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4fb8948d0c0468c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4749,7 +4749,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bedf40353424def"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9056390848e48d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5387,7 +5387,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77c53bfec319469b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93011a58687f41e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6025,7 +6025,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdfc00e098f74361"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d3f2126d5ba492a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6785,7 +6785,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf5999a38b784cdc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcef5278f012c4ebb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7423,7 +7423,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red7553c0f15143d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe80b2991347417b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7923,7 +7923,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2ee6aa86f734c8c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra25b021c89b147de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8668,7 +8668,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64b9763b03824e6b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3a218c6786c47ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9045,7 +9045,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7a1a5de6b3e4d65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d65e79617b64179"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9479,7 +9479,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R916cecef787c4c1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7452113bc561484c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10219,7 +10219,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8656441f7b55401c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R845c003d47fb458c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10959,7 +10959,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf1a8dfa30294e31"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3a6f48a64d04ece"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11393,7 +11393,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94f6d0e29ef3458a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d5daabd5c074a22"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11868,7 +11868,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9b7f1dbff2b40fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd32330c6632c434e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12490,7 +12490,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38aa7a7709a94f30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca7721327f534981"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13300,7 +13300,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7abddd7160984d1d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra99fefa3bd334fd4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13910,7 +13910,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R518bb4ae1d73479f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd76011885de14d47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15751,7 +15751,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc860b6dd7904b86"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R157cba3ccc3a474c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16324,7 +16324,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25b4c2b450df4958"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ed268a4e8a94f02"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16652,7 +16652,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1bce6e089d449f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8809bd2041154d46"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17290,7 +17290,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e2c6b1c7d884ce2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cd016e4ee464229"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17944,7 +17944,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8484f9d8b55b46b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3cebaa181f24855"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18582,7 +18582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69c66ee0769745e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc581fb7528d94e69"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18910,7 +18910,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fbc8b9e6d14444e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc806c678a1e74980"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Nexus_Uprising_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Nexus_Uprising_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rca6beac03e954368"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R9a5f83ff1f604481"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R23df76bee67046b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R9c490112f33c4316"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rf68d7ce13cf545af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R665f2e646aa743b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R9101bc19f2384039"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rc28c2b4112bc4c00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R9b3d768eba1b4f6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R247f5f65195b48a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R379f7a0eea3e4b02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R4c7c1c6ff71e46d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R9466befa05584c52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R2f018f5163044feb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rd897ec71175e4ccf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R765a912e9c4c4253"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rb23c383404a447b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rf0d0f149f5b34161"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rb7219bfb47a44614"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R00a72dd1d3c44628"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Ra15bb6c08f0a4654"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R53cd2c5a3b1240d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rdcbcf5d380b24816"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R03dbbb1b1c8f4e4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R1a25efb6219742cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R02153bf8a20f43d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R1102aed2ba624790"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rd7e5b0d8cf7d4737"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Raadc5faa254c4173"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R1d23582d216c4463"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rc8d27fad30e64c68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R16c3bf4505374e64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R0b3252abd45a46cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Red273a89aa0243a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R662d7f32e1f041f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rc269c1eeeeb7460a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R5d3c57c96b524a7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R9df3d77cf54841bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R8e0dac3127184b1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R3961fa9a3bae4ee7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rc9a66196ca09429f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R81ee599bab6443b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rb8773e235b1f4050"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R2420ffc1c8af460d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R273f54160b434186"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R6e24fa599d6447dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rb356a137c43d4d1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Ra29216a871bb4729"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R05b71b58a4204f72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rbe91261a8f7d49af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R99393c5558c94ca2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R0fe7d7ebcd1a484e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R1f35a6389b0f408c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rca843c29aee94956"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Raa6fcbd182e3488a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R32dc03aea8394845"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4111,7 +4111,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4fb8948d0c0468c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2c1d131a96e4717"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4749,7 +4749,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9056390848e48d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R342032c6003346b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5387,7 +5387,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93011a58687f41e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red8b0f9f780d4269"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6025,7 +6025,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d3f2126d5ba492a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66cc1b8607474b5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6785,7 +6785,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcef5278f012c4ebb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra978fc1310cc4fdd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7423,7 +7423,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe80b2991347417b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a158ceb4440484b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7923,7 +7923,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra25b021c89b147de"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f1c049b87184838"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8668,7 +8668,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3a218c6786c47ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6c89318576442eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9045,7 +9045,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d65e79617b64179"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd1c13f646b7480a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9479,7 +9479,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7452113bc561484c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4aca4a9baeb4a5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10219,7 +10219,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R845c003d47fb458c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a6d47afe9424aa2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10959,7 +10959,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3a6f48a64d04ece"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7db86bfa6e04b27"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11393,7 +11393,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d5daabd5c074a22"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra39f752bd750438c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11868,7 +11868,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd32330c6632c434e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra649483bda9f41d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12490,7 +12490,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca7721327f534981"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26c1eb7ebba64617"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13300,7 +13300,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra99fefa3bd334fd4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40d8df631e004981"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13910,7 +13910,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd76011885de14d47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36c418febf9041a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15751,7 +15751,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R157cba3ccc3a474c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf92c41fa9e0a4d78"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16324,7 +16324,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ed268a4e8a94f02"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6932085067ec4a84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16652,7 +16652,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8809bd2041154d46"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb29dab8113943df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17290,7 +17290,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cd016e4ee464229"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R155ddf5ef00347ad"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17944,7 +17944,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3cebaa181f24855"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb579f4b863344a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18582,7 +18582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc581fb7528d94e69"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00269b7e41dc4245"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18910,7 +18910,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc806c678a1e74980"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0a5687748964748"/>
   </x:tableParts>
 </x:worksheet>
 </file>